--- a/02. Planificacion/Backlog del Sprint.xlsx
+++ b/02. Planificacion/Backlog del Sprint.xlsx
@@ -3800,7 +3800,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="G25" s="1">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="G26" s="1">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="G27" s="1">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="G28" s="1">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="G29" s="1">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="G30" s="1">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="G31" s="1">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="G32" s="1">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="G33" s="1">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="G34" s="1">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="G35" s="1">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="G36" s="1">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="G37" s="1">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="G38" s="1">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="G39" s="1">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Por Hacer</t>
+          <t xml:space="preserve">Terminado</t>
         </is>
       </c>
       <c r="G40" s="1">
